--- a/dictionary_final.xlsx
+++ b/dictionary_final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\掛布一世\Desktop\original archive trial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1E833FB-814B-44A7-9EEC-5C75162D8451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE50E748-C3D4-4528-BE99-2C860ED651B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020年" sheetId="8" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2725" uniqueCount="2204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2726" uniqueCount="2205">
   <si>
     <t>【10人コラボ】ボンバーマンRオンライン～俺たち爆弾家族～【ガヤガヤ】</t>
   </si>
@@ -6713,6 +6713,10 @@
   </si>
   <si>
     <t>010122-2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>trial1.html?v=1898451786&amp;d=081423&amp;s=3</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -11929,6 +11933,9 @@
       <c r="F114" t="s">
         <v>1036</v>
       </c>
+      <c r="G114" t="s">
+        <v>2204</v>
+      </c>
       <c r="K114" s="1" t="s">
         <v>1037</v>
       </c>

--- a/dictionary_final.xlsx
+++ b/dictionary_final.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88290D70-2426-46B5-8F6C-307004DAA32B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12072" yWindow="1068" windowWidth="10872" windowHeight="10812" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020年" sheetId="1" r:id="rId1"/>
@@ -9985,7 +9985,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/dictionary_final.xlsx
+++ b/dictionary_final.xlsx
@@ -16061,7 +16061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K155"/>
+  <dimension ref="A1:K159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
     <col width="8.88671875" customWidth="1" style="1" min="11" max="11"/>
@@ -18925,6 +18925,74 @@
         </is>
       </c>
     </row>
+    <row r="156">
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>【switch】メタルギアソリッド4</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>▶ クリップ</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>1日目(10/7)</t>
+        </is>
+      </c>
+      <c r="K156" s="1" t="inlineStr">
+        <is>
+          <t>100726</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2日目(10/9)</t>
+        </is>
+      </c>
+      <c r="K157" s="1" t="inlineStr">
+        <is>
+          <t>100926</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>3日目(10/13)</t>
+        </is>
+      </c>
+      <c r="K158" s="1" t="inlineStr">
+        <is>
+          <t>101326</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>MSXグラディウスシリーズをたしなむ配信【STG配信祭】</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>▶ クリップ</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>単発(10/11)</t>
+        </is>
+      </c>
+      <c r="K159" s="1" t="inlineStr">
+        <is>
+          <t>101126</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/dictionary_final.xlsx
+++ b/dictionary_final.xlsx
@@ -5210,7 +5210,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>trial1.html?v=LTcD8Cc3whE&amp;d=070922&amp;s=3</t>
+          <t>trial1.html?v=LTcD8Cc3whE&amp;d=070922-2&amp;s=3</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>trial1.html?v=V1zehxuQ5us&amp;d=082422&amp;s=3</t>
+          <t>trial1.html?v=V1zehxuQ5us&amp;d=082122&amp;s=3</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>trial1.html?v=uf5cQzQvTws&amp;d=040723&amp;s=3</t>
+          <t>trial1.html?v=uf5cQzQvTws&amp;d=040723-2&amp;s=3</t>
         </is>
       </c>
       <c r="K51" s="1" t="inlineStr">
@@ -12110,7 +12110,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>trial1.html?v=iY_fDoC0pYk&amp;d=040924&amp;s=3</t>
+          <t>trial1.html?v=iY_fDoC0pYk&amp;d=040824&amp;s=3</t>
         </is>
       </c>
       <c r="K58" s="1" t="inlineStr">
@@ -13879,7 +13879,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>trial1.html?v=qJVZzQLz5UI&amp;d=111624&amp;s=3</t>
+          <t>trial1.html?v=qJVZzQLz5UI&amp;d=111724&amp;s=3</t>
         </is>
       </c>
       <c r="K165" s="1" t="inlineStr">
@@ -13896,7 +13896,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>trial1.html?v=dpT8md18-ss&amp;d=111724&amp;s=3</t>
+          <t>trial1.html?v=dpT8md18-ss&amp;d=111724-2&amp;s=3</t>
         </is>
       </c>
       <c r="K166" s="1" t="inlineStr">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>trial1.html?v=ZzavHeEb3mo&amp;d=041925&amp;s=3</t>
+          <t>trial1.html?v=ZzavHeEb3mo&amp;d=041925-2&amp;s=3</t>
         </is>
       </c>
       <c r="K55" s="1" t="inlineStr">
@@ -15665,7 +15665,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>trial1.html?v=xZ22fBwQpbA&amp;d=053025&amp;s=3</t>
+          <t>trial1.html?v=xZ22fBwQpbA&amp;d=053025-2&amp;s=3</t>
         </is>
       </c>
       <c r="K78" s="1" t="inlineStr">
@@ -16061,7 +16061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K159"/>
+  <dimension ref="A1:K162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
     <col width="8.88671875" customWidth="1" style="1" min="11" max="11"/>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>trial1.html?v=JKaIKUHjXQQ&amp;d=011726&amp;s=3</t>
+          <t>trial1.html?v=JKaIKUHjXQQ&amp;d=011726-2&amp;s=3</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>trial1.html?v=el-aBl1YU0U&amp;d=021026&amp;s=3</t>
+          <t>trial1.html?v=el-aBl1YU0U&amp;d=021026&amp;s=-52</t>
         </is>
       </c>
       <c r="K19" s="1" t="inlineStr">
@@ -16426,7 +16426,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>trial1.html?v=GZWgx9f4I6w&amp;d=021126&amp;s=3</t>
+          <t>trial1.html?v=GZWgx9f4I6w&amp;d=021126&amp;s=-13</t>
         </is>
       </c>
       <c r="K20" s="1" t="inlineStr">
@@ -16443,7 +16443,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>trial1.html?v=v9kn-7z47Z0&amp;d=021326&amp;s=3</t>
+          <t>trial1.html?v=v9kn-7z47Z0&amp;d=021326&amp;s=-29</t>
         </is>
       </c>
       <c r="K21" s="1" t="inlineStr">
@@ -16460,7 +16460,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>trial1.html?v=_cXKAlq2Hmo&amp;d=021426&amp;s=3</t>
+          <t>trial1.html?v=_cXKAlq2Hmo&amp;d=021426&amp;s=-40</t>
         </is>
       </c>
       <c r="K22" s="1" t="inlineStr">
@@ -16519,7 +16519,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>trial1.html?v=YELcciIX__8&amp;d=021526&amp;s=3</t>
+          <t>trial1.html?v=YELcciIX__8&amp;d=021526&amp;s=-39</t>
         </is>
       </c>
       <c r="K24" s="1" t="inlineStr">
@@ -16536,7 +16536,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>trial1.html?v=4EgsEAjSGGY&amp;d=021726&amp;s=3</t>
+          <t>trial1.html?v=4EgsEAjSGGY&amp;d=021726&amp;s=-118</t>
         </is>
       </c>
       <c r="K25" s="1" t="inlineStr">
@@ -16553,7 +16553,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>trial1.html?v=myy45f9mho4&amp;d=021926&amp;s=3</t>
+          <t>trial1.html?v=myy45f9mho4&amp;d=021926&amp;s=-58</t>
         </is>
       </c>
       <c r="K26" s="1" t="inlineStr">
@@ -16570,7 +16570,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>trial1.html?v=XjpA_EI2Aus&amp;d=022026&amp;s=3</t>
+          <t>trial1.html?v=XjpA_EI2Aus&amp;d=022026&amp;s=-27</t>
         </is>
       </c>
       <c r="K27" s="1" t="inlineStr">
@@ -16587,7 +16587,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>trial1.html?v=FB4Djt4-fFo&amp;d=022526&amp;s=3</t>
+          <t>trial1.html?v=FB4Djt4-fFo&amp;d=022526&amp;s=-14</t>
         </is>
       </c>
       <c r="K28" s="1" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>trial1.html?v=3OylPu_VvDg&amp;d=022726&amp;s=3</t>
+          <t>trial1.html?v=3OylPu_VvDg&amp;d=022726&amp;s=-34</t>
         </is>
       </c>
       <c r="K29" s="1" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>trial1.html?v=YKV5iYC-g_Y&amp;d=022126&amp;s=3</t>
+          <t>trial1.html?v=YKV5iYC-g_Y&amp;d=022126&amp;s=-21</t>
         </is>
       </c>
       <c r="K30" s="1" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>trial1.html?v=bOnw_eF8pbE&amp;d=022326&amp;s=3</t>
+          <t>trial1.html?v=bOnw_eF8pbE&amp;d=022326&amp;s=-59</t>
         </is>
       </c>
       <c r="K31" s="1" t="inlineStr">
@@ -16763,7 +16763,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>trial1.html?v=qw3zyIoDfj4&amp;d=031326&amp;s=3</t>
+          <t>trial1.html?v=qw3zyIoDfj4&amp;d=031326&amp;s=-56</t>
         </is>
       </c>
       <c r="K36" s="1" t="inlineStr">
@@ -16780,7 +16780,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>trial1.html?v=9kYnO_80jxM&amp;d=031426&amp;s=3</t>
+          <t>trial1.html?v=9kYnO_80jxM&amp;d=031426&amp;s=-27</t>
         </is>
       </c>
       <c r="K37" s="1" t="inlineStr">
@@ -16797,7 +16797,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>trial1.html?v=y8agZQPCepY&amp;d=031526&amp;s=3</t>
+          <t>trial1.html?v=y8agZQPCepY&amp;d=031526&amp;s=-20</t>
         </is>
       </c>
       <c r="K38" s="1" t="inlineStr">
@@ -18462,6 +18462,11 @@
           <t>1日目(8/19)</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>trial1.html?v=R9SGUE9t_Y0&amp;d=081926&amp;s=3</t>
+        </is>
+      </c>
       <c r="K124" s="1" t="inlineStr">
         <is>
           <t>081926</t>
@@ -18474,6 +18479,11 @@
           <t>2日目(8/20)</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>trial1.html?v=mpFjsPUaxLM&amp;d=082026&amp;s=3</t>
+        </is>
+      </c>
       <c r="K125" s="1" t="inlineStr">
         <is>
           <t>082026</t>
@@ -18486,6 +18496,11 @@
           <t>3日目(8/21)</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>trial1.html?v=yHl4KakfgJA&amp;d=082126&amp;s=3</t>
+        </is>
+      </c>
       <c r="K126" s="1" t="inlineStr">
         <is>
           <t>082126</t>
@@ -18508,6 +18523,11 @@
           <t>単発(8/22)</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>trial1.html?v=Y93M-TFxLrs&amp;d=082226&amp;s=3</t>
+        </is>
+      </c>
       <c r="K127" s="1" t="inlineStr">
         <is>
           <t>082226</t>
@@ -18530,6 +18550,11 @@
           <t>1日目(8/25)</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>trial1.html?v=0mohvtlUmWg&amp;d=082526&amp;s=3</t>
+        </is>
+      </c>
       <c r="K128" s="1" t="inlineStr">
         <is>
           <t>082526</t>
@@ -18542,6 +18567,11 @@
           <t>2日目(8/27)</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>trial1.html?v=cADNbqxn6Ow&amp;d=082726&amp;s=3</t>
+        </is>
+      </c>
       <c r="K129" s="1" t="inlineStr">
         <is>
           <t>082726</t>
@@ -18554,6 +18584,11 @@
           <t>3日目(8/28)</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>trial1.html?v=kmc_R83AeBc&amp;d=082826&amp;s=3</t>
+        </is>
+      </c>
       <c r="K130" s="1" t="inlineStr">
         <is>
           <t>082826</t>
@@ -18566,6 +18601,11 @@
           <t>4日目(8/30深夜)</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>trial1.html?v=PwmBOQN1itg&amp;d=083026&amp;s=3</t>
+        </is>
+      </c>
       <c r="K131" s="1" t="inlineStr">
         <is>
           <t>083026</t>
@@ -18685,6 +18725,11 @@
           <t>最終回(9/8)</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>trial1.html?v=4SSxHgN3cRI&amp;d=090826&amp;s=3</t>
+        </is>
+      </c>
       <c r="K138" s="1" t="inlineStr">
         <is>
           <t>090826</t>
@@ -18707,6 +18752,11 @@
           <t>単発(9/9)</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>trial1.html?v=3zlW4gIma_Y&amp;d=090926&amp;s=3</t>
+        </is>
+      </c>
       <c r="K139" s="1" t="inlineStr">
         <is>
           <t>090926</t>
@@ -18729,6 +18779,11 @@
           <t>1日目(9/11)</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>trial1.html?v=9GU5kKsjTdg&amp;d=091126&amp;s=3</t>
+        </is>
+      </c>
       <c r="K140" s="1" t="inlineStr">
         <is>
           <t>091126</t>
@@ -18741,6 +18796,11 @@
           <t>2日目(9/13)</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>trial1.html?v=neLBocE7Amg&amp;d=091326&amp;s=3</t>
+        </is>
+      </c>
       <c r="K141" s="1" t="inlineStr">
         <is>
           <t>091326</t>
@@ -18753,6 +18813,11 @@
           <t>3日目(9/16)</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>trial1.html?v=9ZeZGwGBc3I&amp;d=091626&amp;s=3</t>
+        </is>
+      </c>
       <c r="K142" s="1" t="inlineStr">
         <is>
           <t>091626</t>
@@ -18765,6 +18830,11 @@
           <t>4日目(9/18)</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>trial1.html?v=wlYDrFFbBec&amp;d=091826&amp;s=3</t>
+        </is>
+      </c>
       <c r="K143" s="1" t="inlineStr">
         <is>
           <t>091826</t>
@@ -18777,6 +18847,11 @@
           <t>5日目(9/20)</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>trial1.html?v=4lPPYmEzSY0&amp;d=092026&amp;s=3</t>
+        </is>
+      </c>
       <c r="K144" s="1" t="inlineStr">
         <is>
           <t>092026</t>
@@ -18990,6 +19065,37 @@
       <c r="K159" s="1" t="inlineStr">
         <is>
           <t>101126</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>5日目(10/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>6日目(10/19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>MSXグラディウスシリーズをたしなむ配信【STG配信祭】</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>▶ クリップ</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>単発(10/11)</t>
         </is>
       </c>
     </row>

--- a/dictionary_final.xlsx
+++ b/dictionary_final.xlsx
@@ -16061,7 +16061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K162"/>
+  <dimension ref="A1:K165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
     <col width="8.88671875" customWidth="1" style="1" min="11" max="11"/>
@@ -19074,6 +19074,11 @@
           <t>5日目(10/18)</t>
         </is>
       </c>
+      <c r="K160" s="1" t="inlineStr">
+        <is>
+          <t>101826</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="F161" t="inlineStr">
@@ -19081,6 +19086,11 @@
           <t>6日目(10/19)</t>
         </is>
       </c>
+      <c r="K161" s="1" t="inlineStr">
+        <is>
+          <t>101926</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="B162" t="inlineStr">
@@ -19096,6 +19106,57 @@
       <c r="F162" t="inlineStr">
         <is>
           <t>単発(10/11)</t>
+        </is>
+      </c>
+      <c r="K162" s="1" t="inlineStr">
+        <is>
+          <t>101126</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>【FDS】迷宮寺院ダババ</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>▶ クリップ</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>1日目(10/21)</t>
+        </is>
+      </c>
+      <c r="K163" s="1" t="inlineStr">
+        <is>
+          <t>102126</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2日目(10/22)</t>
+        </is>
+      </c>
+      <c r="K164" s="1" t="inlineStr">
+        <is>
+          <t>102226</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>3日目(10/25)</t>
+        </is>
+      </c>
+      <c r="K165" s="1" t="inlineStr">
+        <is>
+          <t>102526</t>
         </is>
       </c>
     </row>
